--- a/onedrive/DiegoRC/Concentrado_ID_profesores.xlsx
+++ b/onedrive/DiegoRC/Concentrado_ID_profesores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B3184B-8B00-4938-A2DA-C48070399BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB522F-422E-4752-B45F-9F9EA9C6D5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="1328" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profesores" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -447,13 +447,79 @@
   </si>
   <si>
     <t>YASSER FERMAN ORTIZ CASTILLO</t>
+  </si>
+  <si>
+    <t>Juan Manuel Ramírez Contreras</t>
+  </si>
+  <si>
+    <t>Maxim Ivanov Todorov</t>
+  </si>
+  <si>
+    <t>Vianey Cordoba Salazar</t>
+  </si>
+  <si>
+    <t>Uvencio José Giménez Mujica</t>
+  </si>
+  <si>
+    <t>Guadalupe Eunice Campiran</t>
+  </si>
+  <si>
+    <t>Valeria Magali Rocha Rocha</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL RAMIREZ CONTRERAS</t>
+  </si>
+  <si>
+    <t>MAXIM IVANOV TODOROV</t>
+  </si>
+  <si>
+    <t>VIANEY CORDOBA SALAZAR</t>
+  </si>
+  <si>
+    <t>UVENCIO JOSE GIMENEZ MUJICA</t>
+  </si>
+  <si>
+    <t>ALFREDO EFRAIN ARCEO</t>
+  </si>
+  <si>
+    <t>GLADYS DENISSE SALGADO SUAREZ</t>
+  </si>
+  <si>
+    <t>SARA RODRIGUEZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>EDUARDO HERNANDEZ MONTERO</t>
+  </si>
+  <si>
+    <t>GUADALUPE EUNICE CAMPIRAN</t>
+  </si>
+  <si>
+    <t>VALERIA MAGALI ROCHA ROCHA</t>
+  </si>
+  <si>
+    <t>Eduardo Hernández Montero</t>
+  </si>
+  <si>
+    <t>Sara Rodríguez Rodríguez</t>
+  </si>
+  <si>
+    <t>Alfredo Efraín Arceo</t>
+  </si>
+  <si>
+    <t>LUCILA MUÑIZ MERINO</t>
+  </si>
+  <si>
+    <t>Lucila Muñiz Merino</t>
+  </si>
+  <si>
+    <t>Gladys Denisse Salgado Suárez</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,8 +571,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:C68" totalsRowShown="0">
-  <autoFilter ref="A1:C68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:C79" totalsRowShown="0">
+  <autoFilter ref="A1:C79" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C79">
+    <sortCondition ref="B2:B79"/>
+  </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre de profesor"/>
@@ -803,14 +872,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:C79"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
-    <col min="2" max="3" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.73046875" customWidth="1"/>
+    <col min="2" max="3" width="40.73046875" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>22472</v>
       </c>
@@ -832,729 +903,850 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
+        <v>15282</v>
+      </c>
+      <c r="B3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4">
         <v>23852</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
         <v>25510</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
         <v>22503</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
         <v>22471</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
         <v>23885</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9">
         <v>22097</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>22473</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11">
         <v>23149</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12">
         <v>21815</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13">
         <v>18269</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14">
         <v>23411</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15">
         <v>21852</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16">
         <v>23425</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17">
         <v>21779</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>31</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18">
         <v>22767</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19">
         <v>23836</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20">
         <v>23468</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21">
         <v>21228</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22">
         <v>23152</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23">
         <v>26317</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24">
         <v>16164</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>24510</v>
+      </c>
+      <c r="B25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26">
         <v>23452</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" t="s">
         <v>47</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27">
         <v>25843</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" t="s">
         <v>49</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28">
         <v>24097</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C28" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29">
         <v>22446</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30">
         <v>23824</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31">
         <v>23835</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32">
         <v>23978</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>59</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C32" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>23837</v>
+      </c>
+      <c r="B33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>23466</v>
+      </c>
+      <c r="B34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35">
         <v>22109</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B35" t="s">
         <v>61</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C35" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36">
         <v>25496</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B36" t="s">
         <v>63</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37">
         <v>23442</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B37" t="s">
         <v>65</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C37" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38">
         <v>23153</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B38" t="s">
         <v>67</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C38" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>23874</v>
+      </c>
+      <c r="B39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>22091</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41">
         <v>24086</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B41" t="s">
         <v>69</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C41" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36">
-        <v>23874</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37">
-        <v>22091</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42">
         <v>21854</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B42" t="s">
         <v>75</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C42" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43">
         <v>26078</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B43" t="s">
         <v>77</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C43" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>23133</v>
+      </c>
+      <c r="B44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45">
         <v>22521</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B45" t="s">
         <v>79</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C45" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46">
         <v>25487</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B46" t="s">
         <v>81</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C46" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47">
         <v>25093</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B47" t="s">
         <v>83</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C47" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48">
         <v>24085</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B48" t="s">
         <v>85</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C48" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49">
         <v>23453</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B49" t="s">
         <v>87</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C49" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>24780</v>
+      </c>
+      <c r="B50" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51">
         <v>21853</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B51" t="s">
         <v>89</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C51" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52">
         <v>21192</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B52" t="s">
         <v>91</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C52" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53">
         <v>20792</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B53" t="s">
         <v>93</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C53" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54">
         <v>23096</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B54" t="s">
         <v>95</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C54" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55">
         <v>21756</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B55" t="s">
         <v>97</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C55" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>12516</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57">
         <v>23162</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B57" t="s">
         <v>99</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C57" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58">
         <v>24013</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B58" t="s">
         <v>101</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C58" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59">
         <v>25531</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B59" t="s">
         <v>103</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C59" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60">
         <v>23148</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B60" t="s">
         <v>105</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C60" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61">
         <v>23434</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B61" t="s">
         <v>107</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C61" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62">
         <v>23839</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B62" t="s">
         <v>109</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C62" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63">
         <v>23823</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B63" t="s">
         <v>111</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C63" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64">
         <v>24117</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B64" t="s">
         <v>113</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C64" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65">
         <v>20529</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B65" t="s">
         <v>115</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C65" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66">
         <v>21262</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B66" t="s">
         <v>117</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C66" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67">
         <v>22114</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B67" t="s">
         <v>119</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C67" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68">
         <v>25503</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B68" t="s">
         <v>121</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C68" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69">
         <v>22115</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B69" t="s">
         <v>123</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C69" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70">
         <v>23859</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B70" t="s">
         <v>125</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C70" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71">
         <v>23887</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B71" t="s">
         <v>127</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C71" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>20530</v>
+      </c>
+      <c r="B72" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73">
         <v>25494</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B73" t="s">
         <v>129</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C73" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>25096</v>
+      </c>
+      <c r="B74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>20566</v>
+      </c>
+      <c r="B75" t="s">
+        <v>142</v>
+      </c>
+      <c r="C75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>23218</v>
+      </c>
+      <c r="B76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A77">
         <v>23897</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B77" t="s">
         <v>131</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C77" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A78">
         <v>24827</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B78" t="s">
         <v>133</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C78" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A79">
         <v>23799</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B79" t="s">
         <v>135</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C79" t="s">
         <v>136</v>
       </c>
     </row>
